--- a/artfynd/A 57357-2024 artfynd.xlsx
+++ b/artfynd/A 57357-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56071528</v>
+        <v>56071529</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>670994.1901840505</v>
+        <v>670995</v>
       </c>
       <c r="R2" t="n">
-        <v>7124771.889142835</v>
+        <v>7124809</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2015-10-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-10-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +779,7 @@
         <v>56071530</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -835,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>671013.1293321209</v>
+        <v>671013</v>
       </c>
       <c r="R3" t="n">
-        <v>7124848.000389444</v>
+        <v>7124848</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,19 +848,9 @@
           <t>2015-10-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-10-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,37 +878,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>56071529</v>
+        <v>56071528</v>
       </c>
       <c r="B4" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -952,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>670995.1894103504</v>
+        <v>670994</v>
       </c>
       <c r="R4" t="n">
-        <v>7124809.038972602</v>
+        <v>7124772</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,19 +950,9 @@
           <t>2015-10-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-10-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 57357-2024 artfynd.xlsx
+++ b/artfynd/A 57357-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56071529</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56071530</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,8 +991,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56071528</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>